--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.6290322580645161</v>
+        <v>0.75</v>
       </c>
       <c r="B2">
-        <v>0.07575757575757576</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4084507042253521</v>
+        <v>0.4357142857142857</v>
       </c>
       <c r="D2">
-        <v>0.65625</v>
+        <v>0.6370967741935484</v>
       </c>
       <c r="E2">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G2">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.75</v>
+        <v>0.7627118644067796</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4357142857142857</v>
+        <v>0.4428571428571428</v>
       </c>
       <c r="D2">
-        <v>0.6370967741935484</v>
+        <v>0.6341463414634146</v>
       </c>
       <c r="E2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F2">
         <v>64</v>
       </c>
       <c r="G2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
